--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6E327A-1ACC-4EF9-B829-B9C48772433A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7789893-6744-4DCF-BB89-6BFF62866AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="351">
   <si>
     <t>武器</t>
   </si>
@@ -1053,6 +1053,67 @@
   </si>
   <si>
     <t>让受影响的敌人中毒，18秒内造成120点伤害；炼金桌制作，且概率失败变为蘑菇浸剂；远程武器；</t>
+  </si>
+  <si>
+    <t>烈焰匕首</t>
+  </si>
+  <si>
+    <t>10 火伤</t>
+  </si>
+  <si>
+    <t>待测</t>
+  </si>
+  <si>
+    <t>杀死敌人后，造成额外2点火焰伤害，持续20秒，这20秒内每杀一个敌人，火焰伤害就增加2，20秒后回到初始的10点</t>
+  </si>
+  <si>
+    <t>元素熔炉配方：火把*1 小型火焰精华*5 硝酸钾*1 碎铜片*20</t>
+  </si>
+  <si>
+    <t>元素熔炉配方1：匕首*1 小型火焰精华*10 硝酸钾*2 碎铜片*5
+元素熔炉配方2：也门双刃弯刀*1 小型火焰精华*10 硝酸钾*2 碎铜片*5
+元素熔炉配方3：破刃剑*1 小型火焰精华*10 硝酸钾*2 碎铜片*5
+元素熔炉配方4：耐用匕首*1 小型火焰精华*10 硝酸钾*2 碎铜片*5</t>
+  </si>
+  <si>
+    <t>元素熔炉配方1：法兰锤*1 火焰精华*10 硝酸钾*10 蜡烛*10
+元素熔炉配方2：见习修士锤*1 火焰精华*10 硝酸钾*10 蜡烛*10</t>
+  </si>
+  <si>
+    <t>元素熔炉配方：复合弓*1 火焰精华*10 硝酸钾*10 蜡烛*10</t>
+  </si>
+  <si>
+    <t>元素熔炉配方：青铜矛*1 大型火焰精华*10 硝酸钾*15 极好的武器油*5</t>
+  </si>
+  <si>
+    <t>葬火堆</t>
+  </si>
+  <si>
+    <t>烈焰吐息</t>
+  </si>
+  <si>
+    <t>击杀敌人会对能见范围内所有敌人造成周期性火焰伤害200点，即4*50点燃</t>
+  </si>
+  <si>
+    <t>击中目标时，持续5秒，一共造成200点火焰伤害，即5*40点燃</t>
+  </si>
+  <si>
+    <t>元素熔炉配方：被咒棒子*1 大型火焰精华*20 硝酸钾*20 4级火焰卷轴*2</t>
+  </si>
+  <si>
+    <t>元素熔炉配方：重弩*1 大型火焰精华*20 硝酸钾*20 机械装置*20</t>
+  </si>
+  <si>
+    <t>火焰誓言</t>
+  </si>
+  <si>
+    <t>60 火伤</t>
+  </si>
+  <si>
+    <t>元素熔炉配方：狂战士战斧*1 大型火焰精华*20 硝酸钾*20 纯银*20</t>
+  </si>
+  <si>
+    <t>每次攻击都会给自己叠加一层点燃，每层持续37秒，造成 20*3共60点火焰伤害。身上每有一层点燃，这把武器的火焰伤害就+3。举例：以每秒一次的频率持续攻击，可稳定维持37层，武器火焰伤害从60提升到171，同时你自己每秒承受约60点点燃伤害。若攻击37秒后停手，最后一层还要再烧37秒，累计自伤2220点。全套冰霜护甲可做到不受任何点燃伤害。</t>
   </si>
 </sst>
 </file>
@@ -1737,20 +1798,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1763,19 +1812,10 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1796,27 +1836,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1826,18 +1851,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1845,13 +1861,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1868,13 +1878,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1884,21 +1888,12 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1950,17 +1945,59 @@
     <xf numFmtId="0" fontId="9" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2304,3205 +2341,3317 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396CB4A7-922E-403D-B02B-B84252EDCF5F}">
-  <dimension ref="A1:L142"/>
+  <dimension ref="A1:L146"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.796875" customWidth="1"/>
     <col min="2" max="2" width="16.46484375" customWidth="1"/>
     <col min="3" max="3" width="10.59765625" customWidth="1"/>
-    <col min="7" max="7" width="30.86328125" customWidth="1"/>
-    <col min="8" max="8" width="49.9296875" customWidth="1"/>
+    <col min="7" max="7" width="52.6640625" customWidth="1"/>
+    <col min="8" max="8" width="59" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21.4" thickBot="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="58" t="s">
         <v>288</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="60"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="13.9">
+    <row r="3" spans="1:12">
       <c r="A3" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3">
+      <c r="C3" s="54"/>
+      <c r="D3" s="55">
         <v>1.4</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="55">
         <v>1</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="21"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="32"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="55">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="55">
         <v>1.2</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="55" t="s">
         <v>311</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="13.9">
+    <row r="5" spans="1:12">
       <c r="A5" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="53">
         <v>8</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3">
+      <c r="C5" s="54"/>
+      <c r="D5" s="55">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="55">
         <v>1.2</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="53">
         <v>50</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="21" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="53">
         <v>8</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3">
+      <c r="C6" s="54"/>
+      <c r="D6" s="55">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="55">
         <v>1.2</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="53">
         <v>50</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="13.9">
+    <row r="7" spans="1:12">
       <c r="A7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="53">
         <v>9</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3">
+      <c r="C7" s="54"/>
+      <c r="D7" s="55">
         <v>1</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="55">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="53">
         <v>50</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="21" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="53">
         <v>9</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3">
+      <c r="C8" s="54"/>
+      <c r="D8" s="55">
         <v>1</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="55">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="53">
         <v>50</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="21" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="13.9">
+    <row r="9" spans="1:12">
       <c r="A9" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="53">
         <v>12</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="3">
+      <c r="C9" s="54"/>
+      <c r="D9" s="55">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="55">
         <v>1.3</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="53">
         <v>67</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="21" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="13.9">
+    <row r="10" spans="1:12">
       <c r="A10" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="6">
+      <c r="C10" s="54"/>
+      <c r="D10" s="2">
         <v>1.5</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="2">
         <v>1.3</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="2">
         <v>112</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="21"/>
-    </row>
-    <row r="11" spans="1:12" ht="14.25" thickBot="1">
+      <c r="G10" s="54"/>
+      <c r="H10" s="32"/>
+    </row>
+    <row r="11" spans="1:12" ht="13.9" thickBot="1">
       <c r="A11" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="53">
         <v>13</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="6">
+      <c r="C11" s="54"/>
+      <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="2">
         <v>1.2</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="2">
         <v>67</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="23" t="s">
+      <c r="H11" s="21" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="14.25" thickBot="1">
+    <row r="12" spans="1:12" ht="13.9" thickBot="1">
       <c r="A12" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="6">
+      <c r="C12" s="54"/>
+      <c r="D12" s="2">
         <v>0.9</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="2">
         <v>1.4</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="2">
         <v>56</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="23"/>
-      <c r="L12" s="45"/>
+      <c r="H12" s="21"/>
+      <c r="L12" s="27"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="6">
+      <c r="C13" s="54"/>
+      <c r="D13" s="2">
         <v>0.9</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="2">
         <v>1.4</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="2">
         <v>56</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="H13" s="21" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="13.9">
+    <row r="14" spans="1:12">
       <c r="A14" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="6">
+      <c r="C14" s="54"/>
+      <c r="D14" s="2">
         <v>1.7</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="2">
         <v>125</v>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="21"/>
-    </row>
-    <row r="15" spans="1:12" ht="13.9">
-      <c r="A15" s="26" t="s">
+      <c r="G14" s="54"/>
+      <c r="H14" s="32"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="52" t="s">
         <v>296</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="53">
         <v>18</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="6">
+      <c r="C15" s="54"/>
+      <c r="D15" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="2">
         <v>1.3</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="2">
         <v>84</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="54" t="s">
         <v>307</v>
       </c>
-      <c r="H15" s="46" t="s">
+      <c r="H15" s="63" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="13.9">
+    <row r="16" spans="1:12">
       <c r="A16" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="6">
+      <c r="C16" s="54"/>
+      <c r="D16" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="2">
         <v>77</v>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="21"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="32"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="6">
+      <c r="C17" s="54"/>
+      <c r="D17" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="2">
         <v>340</v>
       </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="21"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="32"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="2">
         <v>1.4</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="2">
         <v>1.2</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="2">
         <v>100</v>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="23" t="s">
+      <c r="G18" s="54"/>
+      <c r="H18" s="21" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="24" t="s">
+    <row r="19" spans="1:8" ht="27">
+      <c r="A19" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="2">
         <v>0.8</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="2">
         <v>1.4</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="23" t="s">
+      <c r="G19" s="57" t="s">
+        <v>336</v>
+      </c>
+      <c r="H19" s="21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="14.65">
-      <c r="A20" s="24" t="s">
+    <row r="20" spans="1:8" ht="14.25">
+      <c r="A20" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="55">
         <v>1.4</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="55">
         <v>1.2</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="53">
         <v>77</v>
       </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="23" t="s">
+      <c r="G20" s="54"/>
+      <c r="H20" s="21" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="13.9">
+    <row r="21" spans="1:8">
       <c r="A21" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="6">
+      <c r="C21" s="5"/>
+      <c r="D21" s="2">
         <v>1.2</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="2">
         <v>1.7</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="2">
         <v>84</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="55" t="s">
         <v>310</v>
       </c>
-      <c r="H21" s="21"/>
-    </row>
-    <row r="22" spans="1:8" ht="13.9">
+      <c r="H21" s="32"/>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="6">
+      <c r="C22" s="5"/>
+      <c r="D22" s="2">
         <v>1.4</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="2">
         <v>1.2</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="2">
         <v>100</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="H22" s="21"/>
+      <c r="H22" s="32"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="6">
+      <c r="C23" s="54"/>
+      <c r="D23" s="2">
         <v>1.4</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="2">
         <v>1.2</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="2">
         <v>500</v>
       </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="21"/>
-    </row>
-    <row r="24" spans="1:8" ht="13.9">
-      <c r="A24" s="26" t="s">
+      <c r="G23" s="54"/>
+      <c r="H23" s="32"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="52" t="s">
         <v>295</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="53">
         <v>20</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="15">
+      <c r="C24" s="54"/>
+      <c r="D24" s="8">
         <v>1</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="8">
         <v>1.2</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="8">
         <v>84</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="54" t="s">
         <v>307</v>
       </c>
-      <c r="H24" s="46" t="s">
+      <c r="H24" s="63" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="13.9">
-      <c r="A25" s="20" t="s">
+    <row r="25" spans="1:8" ht="108">
+      <c r="A25" s="52" t="s">
+        <v>332</v>
+      </c>
+      <c r="B25" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="D25" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>337</v>
+      </c>
+      <c r="H25" s="50" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B26" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="3">
+      <c r="C26" s="54"/>
+      <c r="D26" s="55">
         <v>1.2</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E26" s="55">
         <v>1.7</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F26" s="53">
         <v>84</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G26" s="55" t="s">
         <v>310</v>
       </c>
-      <c r="H25" s="23" t="s">
+      <c r="H26" s="21" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="27" t="s">
+    <row r="27" spans="1:8">
+      <c r="A27" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B27" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="3">
+      <c r="C27" s="54"/>
+      <c r="D27" s="55">
         <v>1.4</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E27" s="55">
         <v>1.2</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F27" s="53">
         <v>112</v>
       </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="23" t="s">
+      <c r="G27" s="54"/>
+      <c r="H27" s="21" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="13.9">
-      <c r="A27" s="20" t="s">
+    <row r="28" spans="1:8">
+      <c r="A28" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B28" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="6">
+      <c r="C28" s="5"/>
+      <c r="D28" s="2">
         <v>1.4</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E28" s="2">
         <v>1.2</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F28" s="2">
         <v>100</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G28" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="H27" s="23" t="s">
+      <c r="H28" s="21" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="13.9">
-      <c r="A28" s="20" t="s">
+    <row r="29" spans="1:8">
+      <c r="A29" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B29" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="6">
+      <c r="C29" s="5"/>
+      <c r="D29" s="2">
         <v>1.4</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E29" s="2">
         <v>1.2</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F29" s="2">
         <v>100</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G29" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="H28" s="23" t="s">
+      <c r="H29" s="21" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="13.9">
-      <c r="A29" s="20" t="s">
+    <row r="30" spans="1:8">
+      <c r="A30" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B30" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="6">
+      <c r="C30" s="5"/>
+      <c r="D30" s="2">
         <v>0.7</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E30" s="2">
         <v>2</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F30" s="2">
         <v>42</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G30" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="H29" s="21"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="28" t="s">
+      <c r="H30" s="32"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B31" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="6">
+      <c r="C31" s="5"/>
+      <c r="D31" s="2">
         <v>1.7</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E31" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F31" s="2">
         <v>91</v>
       </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="23" t="s">
+      <c r="G31" s="54"/>
+      <c r="H31" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="29" t="s">
+    <row r="32" spans="1:8">
+      <c r="A32" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B32" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="6">
+      <c r="C32" s="5"/>
+      <c r="D32" s="2">
         <v>1</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E32" s="2">
         <v>1.9</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F32" s="2">
         <v>72</v>
       </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="21"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="24" t="s">
+      <c r="G32" s="54"/>
+      <c r="H32" s="32"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B33" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="6">
+      <c r="C33" s="5"/>
+      <c r="D33" s="2">
         <v>1</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E33" s="2">
         <v>1.9</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F33" s="2">
         <v>250</v>
       </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="21"/>
-    </row>
-    <row r="33" spans="1:8" ht="13.9">
-      <c r="A33" s="30" t="s">
+      <c r="G33" s="54"/>
+      <c r="H33" s="32"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B34" s="2">
         <v>26</v>
       </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="6">
+      <c r="C34" s="5"/>
+      <c r="D34" s="2">
         <v>0.8</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E34" s="2">
         <v>5</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F34" s="2">
         <v>63</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G34" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="H33" s="21" t="s">
+      <c r="H34" s="32" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="13.9">
-      <c r="A34" s="20" t="s">
+    <row r="35" spans="1:8">
+      <c r="A35" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B35" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C34" s="10"/>
-      <c r="D34" s="6">
+      <c r="C35" s="5"/>
+      <c r="D35" s="2">
         <v>1.3</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E35" s="2">
         <v>1.4</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F35" s="2">
         <v>91</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G35" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="H34" s="21"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="24" t="s">
+      <c r="H35" s="32"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B36" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="10"/>
-      <c r="D35" s="6">
+      <c r="C36" s="5"/>
+      <c r="D36" s="2">
         <v>1.3</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E36" s="2">
         <v>1.4</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F36" s="2">
         <v>250</v>
       </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="21"/>
-    </row>
-    <row r="36" spans="1:8" ht="13.9">
-      <c r="A36" s="20" t="s">
+      <c r="G36" s="54"/>
+      <c r="H36" s="32"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B37" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="6">
+      <c r="C37" s="5"/>
+      <c r="D37" s="2">
         <v>0.7</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E37" s="2">
         <v>2</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F37" s="2">
         <v>42</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G37" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="H36" s="23" t="s">
+      <c r="H37" s="21" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="13.9">
-      <c r="A37" s="20" t="s">
+    <row r="38" spans="1:8">
+      <c r="A38" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B38" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="6">
+      <c r="C38" s="5"/>
+      <c r="D38" s="2">
         <v>0.7</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E38" s="2">
         <v>2</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F38" s="2">
         <v>42</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G38" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="H37" s="23" t="s">
+      <c r="H38" s="21" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="13.9">
-      <c r="A38" s="20" t="s">
+    <row r="39" spans="1:8">
+      <c r="A39" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B39" s="2">
         <v>27</v>
       </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="6">
+      <c r="C39" s="5"/>
+      <c r="D39" s="2">
         <v>0.8</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E39" s="2">
         <v>1.9</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F39" s="2">
         <v>50</v>
       </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="21"/>
-    </row>
-    <row r="39" spans="1:8" ht="13.9">
-      <c r="A39" s="20" t="s">
+      <c r="G39" s="54"/>
+      <c r="H39" s="32"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B40" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C39" s="10"/>
-      <c r="D39" s="6">
+      <c r="C40" s="5"/>
+      <c r="D40" s="2">
         <v>1.3</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E40" s="2">
         <v>1.4</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F40" s="2">
         <v>91</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G40" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="H39" s="23" t="s">
+      <c r="H40" s="21" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:8">
+      <c r="A41" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B41" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="6">
+      <c r="C41" s="5"/>
+      <c r="D41" s="2">
         <v>1.4</v>
       </c>
-      <c r="E40" s="6">
+      <c r="E41" s="2">
         <v>1.4</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F41" s="2">
         <v>250</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G41" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="H40" s="23" t="s">
+      <c r="H41" s="21" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="27" t="s">
+    <row r="42" spans="1:8">
+      <c r="A42" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B41" s="6">
+      <c r="B42" s="2">
         <v>30</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C42" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D42" s="2">
         <v>0.8</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E42" s="2">
         <v>7</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F42" s="2">
         <v>46</v>
       </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="23" t="s">
+      <c r="G42" s="54" t="s">
+        <v>339</v>
+      </c>
+      <c r="H42" s="21" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="28.15">
-      <c r="A42" s="71" t="s">
+    <row r="43" spans="1:8" ht="27">
+      <c r="A43" s="49" t="s">
         <v>291</v>
       </c>
-      <c r="B42" s="6">
+      <c r="B43" s="2">
         <v>30</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C43" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D43" s="2">
         <v>0.8</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E43" s="2">
         <v>7</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F43" s="2">
         <v>46</v>
       </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="33" t="s">
+      <c r="G43" s="54"/>
+      <c r="H43" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="31" t="s">
+    <row r="44" spans="1:8">
+      <c r="A44" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B44" s="2">
         <v>30</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C44" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D44" s="2">
         <v>0.8</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E44" s="2">
         <v>7</v>
       </c>
-      <c r="F43" s="6">
+      <c r="F44" s="2">
         <v>56</v>
       </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="23" t="s">
+      <c r="G44" s="54"/>
+      <c r="H44" s="21" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="13.9">
-      <c r="A44" s="20" t="s">
+    <row r="45" spans="1:8">
+      <c r="A45" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B45" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="6">
+      <c r="C45" s="5"/>
+      <c r="D45" s="2">
         <v>1</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E45" s="2">
         <v>1.5</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F45" s="2">
         <v>67</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G45" s="55" t="s">
         <v>97</v>
       </c>
-      <c r="H44" s="21"/>
-    </row>
-    <row r="45" spans="1:8" ht="13.9">
-      <c r="A45" s="20" t="s">
+      <c r="H45" s="32"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B46" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C45" s="10"/>
-      <c r="D45" s="6">
+      <c r="C46" s="5"/>
+      <c r="D46" s="2">
         <v>1</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E46" s="2">
         <v>1.5</v>
       </c>
-      <c r="F45" s="6">
+      <c r="F46" s="2">
         <v>67</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G46" s="55" t="s">
         <v>97</v>
       </c>
-      <c r="H45" s="23" t="s">
+      <c r="H46" s="21" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="13.9">
-      <c r="A46" s="20" t="s">
+    <row r="47" spans="1:8">
+      <c r="A47" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B47" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C46" s="10"/>
-      <c r="D46" s="6">
+      <c r="C47" s="5"/>
+      <c r="D47" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E47" s="2">
         <v>1.4</v>
       </c>
-      <c r="F46" s="6">
+      <c r="F47" s="2">
         <v>77</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="G47" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="H46" s="21"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="24" t="s">
+      <c r="H47" s="32"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B48" s="2">
         <v>35</v>
       </c>
-      <c r="C47" s="10"/>
-      <c r="D47" s="6">
+      <c r="C48" s="5"/>
+      <c r="D48" s="2">
         <v>0.8</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E48" s="2">
         <v>5</v>
       </c>
-      <c r="F47" s="6">
+      <c r="F48" s="2">
         <v>59</v>
       </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="21" t="s">
+      <c r="G48" s="54"/>
+      <c r="H48" s="32" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="13.9">
-      <c r="A48" s="20" t="s">
+    <row r="49" spans="1:8">
+      <c r="A49" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B49" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="6">
+      <c r="C49" s="5"/>
+      <c r="D49" s="2">
         <v>1.2</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E49" s="2">
         <v>1.4</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F49" s="2">
         <v>84</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G49" s="55" t="s">
         <v>107</v>
       </c>
-      <c r="H48" s="21"/>
-    </row>
-    <row r="49" spans="1:8" ht="13.9">
-      <c r="A49" s="20" t="s">
+      <c r="H49" s="32"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B50" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="10"/>
-      <c r="D49" s="6">
+      <c r="C50" s="5"/>
+      <c r="D50" s="2">
         <v>1.3</v>
       </c>
-      <c r="E49" s="6">
+      <c r="E50" s="2">
         <v>1.2</v>
       </c>
-      <c r="F49" s="6">
+      <c r="F50" s="2">
         <v>91</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G50" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="H49" s="21"/>
-    </row>
-    <row r="50" spans="1:8" ht="13.9">
-      <c r="A50" s="20" t="s">
+      <c r="H50" s="32"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B51" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C50" s="10"/>
-      <c r="D50" s="6">
+      <c r="C51" s="5"/>
+      <c r="D51" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E50" s="6">
+      <c r="E51" s="2">
         <v>1.4</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F51" s="2">
         <v>77</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="G51" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="H50" s="23" t="s">
+      <c r="H51" s="21" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="13.9">
-      <c r="A51" s="20" t="s">
+    <row r="52" spans="1:8">
+      <c r="A52" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B52" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="6">
+      <c r="C52" s="5"/>
+      <c r="D52" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E51" s="6">
+      <c r="E52" s="2">
         <v>1.4</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F52" s="2">
         <v>77</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="G52" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="H51" s="23" t="s">
+      <c r="H52" s="21" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="13.9">
-      <c r="A52" s="20" t="s">
+    <row r="53" spans="1:8">
+      <c r="A53" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B53" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="6">
+      <c r="C53" s="5"/>
+      <c r="D53" s="2">
         <v>1.2</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E53" s="2">
         <v>1.4</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F53" s="2">
         <v>84</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="G53" s="55" t="s">
         <v>107</v>
       </c>
-      <c r="H52" s="23" t="s">
+      <c r="H53" s="21" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="13.9">
-      <c r="A53" s="20" t="s">
+    <row r="54" spans="1:8">
+      <c r="A54" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B54" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C53" s="10"/>
-      <c r="D53" s="6">
+      <c r="C54" s="5"/>
+      <c r="D54" s="2">
         <v>1.3</v>
       </c>
-      <c r="E53" s="6">
+      <c r="E54" s="2">
         <v>1.2</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F54" s="2">
         <v>91</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G54" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="H53" s="23" t="s">
+      <c r="H54" s="21" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="13.9">
-      <c r="A54" s="20" t="s">
+    <row r="55" spans="1:8">
+      <c r="A55" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B55" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="6">
+      <c r="C55" s="5"/>
+      <c r="D55" s="2">
         <v>1.3</v>
       </c>
-      <c r="E54" s="6">
+      <c r="E55" s="2">
         <v>1.2</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F55" s="2">
         <v>91</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G55" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="H54" s="23" t="s">
+      <c r="H55" s="21" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="24" t="s">
+    <row r="56" spans="1:8">
+      <c r="A56" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B56" s="2">
         <v>42</v>
       </c>
-      <c r="C55" s="10"/>
-      <c r="D55" s="6">
+      <c r="C56" s="5"/>
+      <c r="D56" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E55" s="6">
+      <c r="E56" s="2">
         <v>1.6</v>
       </c>
-      <c r="F55" s="6">
+      <c r="F56" s="2">
         <v>72</v>
       </c>
-      <c r="G55" s="2"/>
-      <c r="H55" s="21"/>
-    </row>
-    <row r="56" spans="1:8" ht="13.9">
-      <c r="A56" s="20" t="s">
+      <c r="G56" s="54"/>
+      <c r="H56" s="32"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B57" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="6">
+      <c r="C57" s="5"/>
+      <c r="D57" s="2">
         <v>1</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E57" s="2">
         <v>2</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F57" s="2">
         <v>72</v>
       </c>
-      <c r="G56" s="3" t="s">
+      <c r="G57" s="55" t="s">
         <v>126</v>
       </c>
-      <c r="H56" s="21"/>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="24" t="s">
+      <c r="H57" s="32"/>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B58" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C57" s="10"/>
-      <c r="D57" s="6">
+      <c r="C58" s="5"/>
+      <c r="D58" s="2">
         <v>1</v>
       </c>
-      <c r="E57" s="6">
+      <c r="E58" s="2">
         <v>2</v>
       </c>
-      <c r="F57" s="6">
+      <c r="F58" s="2">
         <v>100</v>
       </c>
-      <c r="G57" s="2"/>
-      <c r="H57" s="21"/>
-    </row>
-    <row r="58" spans="1:8" ht="13.9">
-      <c r="A58" s="20" t="s">
+      <c r="G58" s="54"/>
+      <c r="H58" s="32"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="B58" s="6">
+      <c r="B59" s="2">
         <v>45</v>
       </c>
-      <c r="C58" s="10"/>
-      <c r="D58" s="6">
+      <c r="C59" s="5"/>
+      <c r="D59" s="2">
         <v>0.4</v>
       </c>
-      <c r="E58" s="6">
+      <c r="E59" s="2">
         <v>6.5</v>
       </c>
-      <c r="F58" s="6">
+      <c r="F59" s="2">
         <v>35</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G59" s="55" t="s">
         <v>129</v>
       </c>
-      <c r="H58" s="21" t="s">
+      <c r="H59" s="32" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="27" t="s">
+    <row r="60" spans="1:8">
+      <c r="A60" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B60" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C59" s="10"/>
-      <c r="D59" s="6">
+      <c r="C60" s="5"/>
+      <c r="D60" s="2">
         <v>1.5</v>
       </c>
-      <c r="E59" s="6">
+      <c r="E60" s="2">
         <v>1.3</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F60" s="2">
         <v>100</v>
       </c>
-      <c r="G59" s="2"/>
-      <c r="H59" s="32" t="s">
+      <c r="G60" s="54"/>
+      <c r="H60" s="22" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="28" t="s">
+    <row r="61" spans="1:8">
+      <c r="A61" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B61" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="6">
+      <c r="C61" s="5"/>
+      <c r="D61" s="2">
         <v>1</v>
       </c>
-      <c r="E60" s="6">
+      <c r="E61" s="2">
         <v>1.2</v>
       </c>
-      <c r="F60" s="6">
+      <c r="F61" s="2">
         <v>67</v>
       </c>
-      <c r="G60" s="2"/>
-      <c r="H60" s="32" t="s">
+      <c r="G61" s="54"/>
+      <c r="H61" s="22" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="14.65">
-      <c r="A61" s="28" t="s">
+    <row r="62" spans="1:8" ht="14.25">
+      <c r="A62" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B62" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C62" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D62" s="2">
         <v>1.5</v>
       </c>
-      <c r="E61" s="6">
+      <c r="E62" s="2">
         <v>1.3</v>
       </c>
-      <c r="F61" s="6">
+      <c r="F62" s="2">
         <v>67</v>
       </c>
-      <c r="G61" s="2"/>
-      <c r="H61" s="23" t="s">
+      <c r="G62" s="54"/>
+      <c r="H62" s="21" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="14.65">
-      <c r="A62" s="27" t="s">
+    <row r="63" spans="1:8" ht="14.25">
+      <c r="A63" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="B62" s="6">
+      <c r="B63" s="2">
         <v>50</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C63" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D63" s="2">
         <v>1</v>
       </c>
-      <c r="E62" s="6">
+      <c r="E63" s="2">
         <v>1.6</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F63" s="2">
         <v>50</v>
       </c>
-      <c r="G62" s="2"/>
-      <c r="H62" s="23" t="s">
+      <c r="G63" s="54"/>
+      <c r="H63" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27">
-      <c r="A63" s="27" t="s">
+    <row r="64" spans="1:8" ht="25.9" customHeight="1">
+      <c r="A64" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="B63" s="6">
+      <c r="B64" s="2">
         <v>52</v>
       </c>
-      <c r="C63" s="10"/>
-      <c r="D63" s="6">
+      <c r="C64" s="5"/>
+      <c r="D64" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E63" s="6">
+      <c r="E64" s="2">
         <v>1.4</v>
       </c>
-      <c r="F63" s="6">
+      <c r="F64" s="2">
         <v>91</v>
       </c>
-      <c r="G63" s="2"/>
-      <c r="H63" s="33" t="s">
+      <c r="G64" s="54"/>
+      <c r="H64" s="26" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="25.9" customHeight="1">
-      <c r="A64" s="34" t="s">
+    <row r="65" spans="1:8" ht="27" customHeight="1">
+      <c r="A65" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="B64" s="6">
+      <c r="B65" s="2">
         <v>55</v>
       </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="6">
+      <c r="C65" s="5"/>
+      <c r="D65" s="2">
         <v>0.4</v>
       </c>
-      <c r="E64" s="6">
+      <c r="E65" s="2">
         <v>7</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F65" s="2">
         <v>35</v>
       </c>
-      <c r="G64" s="11" t="s">
+      <c r="G65" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="H64" s="52" t="s">
+      <c r="H65" s="31" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="27" customHeight="1">
-      <c r="A65" s="27" t="s">
+    <row r="66" spans="1:8">
+      <c r="A66" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="B65" s="6">
+      <c r="B66" s="2">
         <v>55</v>
       </c>
-      <c r="C65" s="10"/>
-      <c r="D65" s="6">
+      <c r="C66" s="5"/>
+      <c r="D66" s="2">
         <v>1.2</v>
       </c>
-      <c r="E65" s="6">
+      <c r="E66" s="2">
         <v>1.4</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F66" s="2">
         <v>77</v>
       </c>
-      <c r="G65" s="2"/>
-      <c r="H65" s="23" t="s">
+      <c r="G66" s="54"/>
+      <c r="H66" s="21" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="27" t="s">
+    <row r="67" spans="1:8" ht="54">
+      <c r="A67" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="B66" s="6">
+      <c r="B67" s="2">
         <v>55</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C67" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D67" s="2">
         <v>1</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E67" s="2">
         <v>1.6</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F67" s="2">
         <v>67</v>
       </c>
-      <c r="G66" s="2"/>
-      <c r="H66" s="23" t="s">
+      <c r="G67" s="51" t="s">
+        <v>338</v>
+      </c>
+      <c r="H67" s="21" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="27" t="s">
+    <row r="68" spans="1:8">
+      <c r="A68" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B68" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C67" s="10"/>
-      <c r="D67" s="6">
+      <c r="C68" s="5"/>
+      <c r="D68" s="2">
         <v>1.5</v>
       </c>
-      <c r="E67" s="6">
+      <c r="E68" s="2">
         <v>1.3</v>
       </c>
-      <c r="F67" s="6">
+      <c r="F68" s="2">
         <v>67</v>
       </c>
-      <c r="G67" s="2"/>
-      <c r="H67" s="23" t="s">
+      <c r="G68" s="54"/>
+      <c r="H68" s="21" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="27" t="s">
+    <row r="69" spans="1:8">
+      <c r="A69" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B69" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="6">
+      <c r="C69" s="5"/>
+      <c r="D69" s="2">
         <v>1.5</v>
       </c>
-      <c r="E68" s="6">
+      <c r="E69" s="2">
         <v>1.3</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F69" s="2">
         <v>91</v>
       </c>
-      <c r="G68" s="2"/>
-      <c r="H68" s="23" t="s">
+      <c r="G69" s="54"/>
+      <c r="H69" s="21" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" ht="27">
-      <c r="A69" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C69" s="10"/>
-      <c r="D69" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="E69" s="6">
-        <v>1.7</v>
-      </c>
-      <c r="F69" s="6">
-        <v>56</v>
-      </c>
-      <c r="G69" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="H69" s="21"/>
     </row>
     <row r="70" spans="1:8" ht="28.5" customHeight="1">
       <c r="A70" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C70" s="5"/>
+      <c r="D70" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="E70" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="F70" s="2">
+        <v>56</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H70" s="32"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B71" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C70" s="10"/>
-      <c r="D70" s="6">
+      <c r="C71" s="5"/>
+      <c r="D71" s="2">
         <v>1.2</v>
       </c>
-      <c r="E70" s="6">
+      <c r="E71" s="2">
         <v>1.5</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F71" s="2">
         <v>72</v>
       </c>
-      <c r="G70" s="2"/>
-      <c r="H70" s="21"/>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="24" t="s">
+      <c r="G71" s="54"/>
+      <c r="H71" s="32"/>
+    </row>
+    <row r="72" spans="1:8" ht="44.25" customHeight="1">
+      <c r="A72" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B72" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="6">
+      <c r="C72" s="5"/>
+      <c r="D72" s="2">
         <v>1.2</v>
       </c>
-      <c r="E71" s="6">
+      <c r="E72" s="2">
         <v>1.5</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F72" s="2">
         <v>100</v>
       </c>
-      <c r="G71" s="2"/>
-      <c r="H71" s="21"/>
-    </row>
-    <row r="72" spans="1:8" ht="44.25" customHeight="1">
-      <c r="A72" s="28" t="s">
+      <c r="G72" s="54"/>
+      <c r="H72" s="32"/>
+    </row>
+    <row r="73" spans="1:8" ht="21" customHeight="1">
+      <c r="A73" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="B72" s="6">
+      <c r="B73" s="2">
         <v>60</v>
       </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="6">
+      <c r="C73" s="5"/>
+      <c r="D73" s="2">
         <v>0.9</v>
       </c>
-      <c r="E72" s="6">
+      <c r="E73" s="2">
         <v>1.5</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F73" s="2">
         <v>56</v>
       </c>
-      <c r="G72" s="2"/>
-      <c r="H72" s="36" t="s">
+      <c r="G73" s="54"/>
+      <c r="H73" s="26" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="21" customHeight="1">
-      <c r="A73" s="27" t="s">
+    <row r="74" spans="1:8">
+      <c r="A74" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B74" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C73" s="10"/>
-      <c r="D73" s="6">
+      <c r="C74" s="5"/>
+      <c r="D74" s="2">
         <v>0.9</v>
       </c>
-      <c r="E73" s="6">
+      <c r="E74" s="2">
         <v>1.6</v>
       </c>
-      <c r="F73" s="6">
+      <c r="F74" s="2">
         <v>84</v>
       </c>
-      <c r="G73" s="2"/>
-      <c r="H73" s="21"/>
-    </row>
-    <row r="74" spans="1:8" ht="40.5">
-      <c r="A74" s="28" t="s">
+      <c r="G74" s="54"/>
+      <c r="H74" s="32"/>
+    </row>
+    <row r="75" spans="1:8" ht="44.65" customHeight="1">
+      <c r="A75" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B75" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C74" s="10"/>
-      <c r="D74" s="6">
+      <c r="C75" s="5"/>
+      <c r="D75" s="2">
         <v>1.4</v>
       </c>
-      <c r="E74" s="6">
+      <c r="E75" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F74" s="6">
+      <c r="F75" s="2">
         <v>77</v>
       </c>
-      <c r="G74" s="2"/>
-      <c r="H74" s="36" t="s">
+      <c r="G75" s="54"/>
+      <c r="H75" s="26" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="44.65" customHeight="1">
-      <c r="A75" s="27" t="s">
+    <row r="76" spans="1:8">
+      <c r="A76" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="B75" s="6">
+      <c r="B76" s="2">
         <v>60</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C76" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D75" s="6">
+      <c r="D76" s="2">
         <v>1</v>
       </c>
-      <c r="E75" s="6">
+      <c r="E76" s="2">
         <v>1.6</v>
       </c>
-      <c r="F75" s="6">
+      <c r="F76" s="2">
         <v>63</v>
       </c>
-      <c r="G75" s="2"/>
-      <c r="H75" s="37" t="s">
+      <c r="G76" s="54"/>
+      <c r="H76" s="21" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="27" t="s">
+    <row r="77" spans="1:8">
+      <c r="A77" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="B76" s="6">
+      <c r="B77" s="2">
         <v>60</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C77" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D76" s="6">
+      <c r="D77" s="2">
         <v>0.9</v>
       </c>
-      <c r="E76" s="6">
+      <c r="E77" s="2">
         <v>1.8</v>
       </c>
-      <c r="F76" s="6">
+      <c r="F77" s="2">
         <v>56</v>
       </c>
-      <c r="G76" s="2"/>
-      <c r="H76" s="23" t="s">
+      <c r="G77" s="54"/>
+      <c r="H77" s="21" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="14.25">
-      <c r="A77" s="27" t="s">
+    <row r="78" spans="1:8" ht="14.25">
+      <c r="A78" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B78" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C77" s="14" t="s">
+      <c r="C78" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="D77" s="6">
+      <c r="D78" s="2">
         <v>0.9</v>
       </c>
-      <c r="E77" s="6">
+      <c r="E78" s="2">
         <v>1.6</v>
       </c>
-      <c r="F77" s="6">
+      <c r="F78" s="2">
         <v>56</v>
       </c>
-      <c r="G77" s="2"/>
-      <c r="H77" s="23" t="s">
+      <c r="G78" s="54"/>
+      <c r="H78" s="21" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
-      <c r="A78" s="27" t="s">
+    <row r="79" spans="1:8">
+      <c r="A79" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B79" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C79" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D78" s="6">
+      <c r="D79" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E78" s="6">
+      <c r="E79" s="2">
         <v>1.6</v>
       </c>
-      <c r="F78" s="6">
+      <c r="F79" s="2">
         <v>53</v>
       </c>
-      <c r="G78" s="2"/>
-      <c r="H78" s="23" t="s">
+      <c r="G79" s="54"/>
+      <c r="H79" s="21" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="27" t="s">
+    <row r="80" spans="1:8">
+      <c r="A80" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B80" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C80" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D79" s="6">
+      <c r="D80" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E79" s="6">
+      <c r="E80" s="2">
         <v>1.7</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F80" s="2">
         <v>59</v>
       </c>
-      <c r="G79" s="2"/>
-      <c r="H79" s="23" t="s">
+      <c r="G80" s="54"/>
+      <c r="H80" s="21" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27">
-      <c r="A80" s="20" t="s">
+    <row r="81" spans="1:8" ht="28.9" customHeight="1">
+      <c r="A81" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="B81" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C80" s="10"/>
-      <c r="D80" s="6">
+      <c r="C81" s="5"/>
+      <c r="D81" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E80" s="6">
+      <c r="E81" s="2">
         <v>1.7</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F81" s="2">
         <v>59</v>
       </c>
-      <c r="G80" s="12" t="s">
+      <c r="G81" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="H80" s="38"/>
-    </row>
-    <row r="81" spans="1:8" ht="28.9" customHeight="1">
-      <c r="A81" s="27" t="s">
+      <c r="H81" s="64"/>
+    </row>
+    <row r="82" spans="1:8" ht="33" customHeight="1">
+      <c r="A82" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="B81" s="6">
+      <c r="B82" s="2">
         <v>62</v>
       </c>
-      <c r="C81" s="10"/>
-      <c r="D81" s="6">
+      <c r="C82" s="5"/>
+      <c r="D82" s="2">
         <v>1.2</v>
       </c>
-      <c r="E81" s="6">
+      <c r="E82" s="2">
         <v>1.2</v>
       </c>
-      <c r="F81" s="6">
+      <c r="F82" s="2">
         <v>67</v>
       </c>
-      <c r="G81" s="2"/>
-      <c r="H81" s="36" t="s">
+      <c r="G82" s="54"/>
+      <c r="H82" s="26" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="33" customHeight="1">
-      <c r="A82" s="29" t="s">
+    <row r="83" spans="1:8" ht="27.4" customHeight="1">
+      <c r="A83" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B83" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C82" s="10"/>
-      <c r="D82" s="6">
+      <c r="C83" s="5"/>
+      <c r="D83" s="2">
         <v>0.9</v>
       </c>
-      <c r="E82" s="6">
+      <c r="E83" s="2">
         <v>1.7</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F83" s="2">
         <v>56</v>
       </c>
-      <c r="G82" s="11" t="s">
+      <c r="G83" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="H82" s="37" t="s">
+      <c r="H83" s="21" t="s">
         <v>180</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="27.4" customHeight="1">
-      <c r="A83" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="C83" s="10"/>
-      <c r="D83" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="E83" s="6">
-        <v>1.7</v>
-      </c>
-      <c r="F83" s="6">
-        <v>56</v>
-      </c>
-      <c r="G83" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="H83" s="37" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="26.25" customHeight="1">
       <c r="A84" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C84" s="5"/>
+      <c r="D84" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="E84" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="F84" s="2">
+        <v>56</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H84" s="21" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="27.75" customHeight="1">
+      <c r="A85" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B85" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="6">
+      <c r="C85" s="5"/>
+      <c r="D85" s="2">
         <v>0.9</v>
       </c>
-      <c r="E84" s="6">
+      <c r="E85" s="2">
         <v>2</v>
       </c>
-      <c r="F84" s="6">
+      <c r="F85" s="2">
         <v>56</v>
       </c>
-      <c r="G84" s="11" t="s">
+      <c r="G85" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="H84" s="21"/>
-    </row>
-    <row r="85" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A85" s="28" t="s">
+      <c r="H85" s="32"/>
+    </row>
+    <row r="86" spans="1:8" ht="30.75" customHeight="1">
+      <c r="A86" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B86" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C85" s="10"/>
-      <c r="D85" s="6">
+      <c r="C86" s="5"/>
+      <c r="D86" s="2">
         <v>1.2</v>
       </c>
-      <c r="E85" s="6">
+      <c r="E86" s="2">
         <v>1.2</v>
       </c>
-      <c r="F85" s="6">
+      <c r="F86" s="2">
         <v>67</v>
       </c>
-      <c r="G85" s="2"/>
-      <c r="H85" s="36" t="s">
+      <c r="G86" s="54"/>
+      <c r="H86" s="26" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A86" s="24" t="s">
+    <row r="87" spans="1:8">
+      <c r="A87" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="B86" s="6">
+      <c r="B87" s="2">
         <v>65</v>
       </c>
-      <c r="C86" s="10"/>
-      <c r="D86" s="6">
+      <c r="C87" s="5"/>
+      <c r="D87" s="2">
         <v>0.8</v>
       </c>
-      <c r="E86" s="6">
+      <c r="E87" s="2">
         <v>7</v>
       </c>
-      <c r="F86" s="6">
+      <c r="F87" s="2">
         <v>59</v>
       </c>
-      <c r="G86" s="51" t="s">
+      <c r="G87" s="51" t="s">
         <v>309</v>
       </c>
-      <c r="H86" s="37" t="s">
+      <c r="H87" s="21" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
-      <c r="A87" s="24" t="s">
+    <row r="88" spans="1:8">
+      <c r="A88" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="B87" s="6">
+      <c r="B88" s="2">
         <v>65</v>
       </c>
-      <c r="C87" s="10"/>
-      <c r="D87" s="6">
+      <c r="C88" s="5"/>
+      <c r="D88" s="2">
         <v>0.8</v>
       </c>
-      <c r="E87" s="6">
+      <c r="E88" s="2">
         <v>7</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F88" s="2">
         <v>84</v>
       </c>
-      <c r="G87" s="2"/>
-      <c r="H87" s="37" t="s">
+      <c r="G88" s="54"/>
+      <c r="H88" s="21" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="27">
-      <c r="A88" s="29" t="s">
+    <row r="89" spans="1:8" ht="30.4" customHeight="1">
+      <c r="A89" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B89" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C88" s="10"/>
-      <c r="D88" s="6">
+      <c r="C89" s="5"/>
+      <c r="D89" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E88" s="6">
+      <c r="E89" s="2">
         <v>1.7</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F89" s="2">
         <v>59</v>
       </c>
-      <c r="G88" s="12" t="s">
+      <c r="G89" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="H88" s="37" t="s">
+      <c r="H89" s="21" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="30.4" customHeight="1">
-      <c r="A89" s="24" t="s">
+    <row r="90" spans="1:8">
+      <c r="A90" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="B90" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C89" s="10"/>
-      <c r="D89" s="6">
+      <c r="C90" s="5"/>
+      <c r="D90" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E89" s="6">
+      <c r="E90" s="2">
         <v>1.7</v>
       </c>
-      <c r="F89" s="6">
+      <c r="F90" s="2">
         <v>84</v>
       </c>
-      <c r="G89" s="2"/>
-      <c r="H89" s="21"/>
-    </row>
-    <row r="90" spans="1:8" ht="13.9">
-      <c r="A90" s="20" t="s">
+      <c r="G90" s="54"/>
+      <c r="H90" s="32"/>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B91" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C90" s="10"/>
-      <c r="D90" s="6">
+      <c r="C91" s="5"/>
+      <c r="D91" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E90" s="6">
+      <c r="E91" s="2">
         <v>1.8</v>
       </c>
-      <c r="F90" s="6">
+      <c r="F91" s="2">
         <v>63</v>
       </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="21"/>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" s="24" t="s">
+      <c r="G91" s="54"/>
+      <c r="H91" s="32"/>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B92" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C91" s="10"/>
-      <c r="D91" s="6">
+      <c r="C92" s="5"/>
+      <c r="D92" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E91" s="6">
+      <c r="E92" s="2">
         <v>1.8</v>
       </c>
-      <c r="F91" s="6">
+      <c r="F92" s="2">
         <v>91</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="21"/>
-    </row>
-    <row r="92" spans="1:8">
-      <c r="A92" s="28" t="s">
+      <c r="G92" s="54"/>
+      <c r="H92" s="32"/>
+    </row>
+    <row r="93" spans="1:8" ht="27">
+      <c r="A93" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="B93" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C93" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="D92" s="6">
+      <c r="D93" s="2">
         <v>0.9</v>
       </c>
-      <c r="E92" s="6">
+      <c r="E93" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F93" s="2">
         <v>46</v>
       </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="39" t="s">
+      <c r="G93" s="57" t="s">
+        <v>340</v>
+      </c>
+      <c r="H93" s="22" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="28" t="s">
+    <row r="94" spans="1:8">
+      <c r="A94" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="B93" s="6">
+      <c r="B94" s="2">
         <v>70</v>
       </c>
-      <c r="C93" s="7" t="s">
+      <c r="C94" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D93" s="6">
+      <c r="D94" s="2">
         <v>0.8</v>
       </c>
-      <c r="E93" s="6">
+      <c r="E94" s="2">
         <v>1.5</v>
       </c>
-      <c r="F93" s="6">
+      <c r="F94" s="2">
         <v>72</v>
       </c>
-      <c r="G93" s="2"/>
-      <c r="H93" s="40" t="s">
+      <c r="G94" s="54"/>
+      <c r="H94" s="23" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
-      <c r="A94" s="28" t="s">
+    <row r="95" spans="1:8">
+      <c r="A95" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="B94" s="6">
+      <c r="B95" s="2">
         <v>77</v>
       </c>
-      <c r="C94" s="10"/>
-      <c r="D94" s="6">
+      <c r="C95" s="5"/>
+      <c r="D95" s="2">
         <v>0.9</v>
       </c>
-      <c r="E94" s="6">
+      <c r="E95" s="2">
         <v>1.4</v>
       </c>
-      <c r="F94" s="6">
+      <c r="F95" s="2">
         <v>72</v>
       </c>
-      <c r="G94" s="2"/>
-      <c r="H94" s="23" t="s">
+      <c r="G95" s="54"/>
+      <c r="H95" s="21" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
-      <c r="A95" s="27" t="s">
+    <row r="96" spans="1:8" ht="30.75" customHeight="1">
+      <c r="A96" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="B95" s="6">
+      <c r="B96" s="2">
         <v>80</v>
       </c>
-      <c r="C95" s="10"/>
-      <c r="D95" s="6">
+      <c r="C96" s="5"/>
+      <c r="D96" s="2">
         <v>1.3</v>
       </c>
-      <c r="E95" s="6">
+      <c r="E96" s="2">
         <v>1.3</v>
       </c>
-      <c r="F95" s="6">
+      <c r="F96" s="2">
         <v>100</v>
       </c>
-      <c r="G95" s="2"/>
-      <c r="H95" s="37" t="s">
+      <c r="G96" s="54"/>
+      <c r="H96" s="21" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A96" s="28" t="s">
+    <row r="97" spans="1:8" ht="27">
+      <c r="A97" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="B96" s="6">
+      <c r="B97" s="2">
         <v>80</v>
       </c>
-      <c r="C96" s="10"/>
-      <c r="D96" s="6">
+      <c r="C97" s="5"/>
+      <c r="D97" s="2">
         <v>0.8</v>
       </c>
-      <c r="E96" s="6">
+      <c r="E97" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F96" s="6">
+      <c r="F97" s="2">
         <v>50</v>
       </c>
-      <c r="G96" s="2"/>
-      <c r="H96" s="36" t="s">
+      <c r="G97" s="54"/>
+      <c r="H97" s="26" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="13.9">
-      <c r="A97" s="20" t="s">
+    <row r="98" spans="1:8">
+      <c r="A98" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="B97" s="6" t="s">
+      <c r="B98" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C97" s="10"/>
-      <c r="D97" s="6">
+      <c r="C98" s="5"/>
+      <c r="D98" s="2">
         <v>0.9</v>
       </c>
-      <c r="E97" s="6">
+      <c r="E98" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F98" s="2">
         <v>46</v>
       </c>
-      <c r="G97" s="2"/>
-      <c r="H97" s="21"/>
-    </row>
-    <row r="98" spans="1:8">
-      <c r="A98" s="24" t="s">
+      <c r="G98" s="54"/>
+      <c r="H98" s="32"/>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B98" s="6" t="s">
+      <c r="B99" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C98" s="10"/>
-      <c r="D98" s="6">
+      <c r="C99" s="5"/>
+      <c r="D99" s="2">
         <v>0.9</v>
       </c>
-      <c r="E98" s="6">
+      <c r="E99" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F98" s="6">
+      <c r="F99" s="2">
         <v>63</v>
       </c>
-      <c r="G98" s="2"/>
-      <c r="H98" s="21"/>
-    </row>
-    <row r="99" spans="1:8">
-      <c r="A99" s="28" t="s">
+      <c r="G99" s="54"/>
+      <c r="H99" s="32"/>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="B99" s="6" t="s">
+      <c r="B100" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C99" s="7" t="s">
+      <c r="C100" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D99" s="6">
+      <c r="D100" s="2">
         <v>0.9</v>
       </c>
-      <c r="E99" s="6">
+      <c r="E100" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F99" s="6">
+      <c r="F100" s="2">
         <v>46</v>
       </c>
-      <c r="G99" s="2"/>
-      <c r="H99" s="23" t="s">
+      <c r="G100" s="54"/>
+      <c r="H100" s="21" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="28" t="s">
+    <row r="101" spans="1:8">
+      <c r="A101" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="B100" s="6" t="s">
+      <c r="B101" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="C101" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="D100" s="6">
+      <c r="D101" s="2">
         <v>0.9</v>
       </c>
-      <c r="E100" s="6">
+      <c r="E101" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F100" s="6">
+      <c r="F101" s="2">
         <v>46</v>
       </c>
-      <c r="G100" s="3"/>
-      <c r="H100" s="23"/>
-    </row>
-    <row r="101" spans="1:8">
-      <c r="A101" s="28" t="s">
+      <c r="G101" s="55"/>
+      <c r="H101" s="21"/>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="B101" s="6">
+      <c r="B102" s="2">
         <v>83</v>
       </c>
-      <c r="C101" s="10"/>
-      <c r="D101" s="6">
+      <c r="C102" s="5"/>
+      <c r="D102" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E101" s="6">
+      <c r="E102" s="2">
         <v>1.6</v>
       </c>
-      <c r="F101" s="6">
+      <c r="F102" s="2">
         <v>72</v>
       </c>
-      <c r="G101" s="2"/>
-      <c r="H101" s="23" t="s">
+      <c r="G102" s="54"/>
+      <c r="H102" s="21" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
-      <c r="A102" s="27" t="s">
+    <row r="103" spans="1:8">
+      <c r="A103" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="B102" s="6" t="s">
+      <c r="B103" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C102" s="10"/>
-      <c r="D102" s="6">
+      <c r="C103" s="5"/>
+      <c r="D103" s="2">
         <v>0.9</v>
       </c>
-      <c r="E102" s="6">
+      <c r="E103" s="2">
         <v>1.7</v>
       </c>
-      <c r="F102" s="6">
+      <c r="F103" s="2">
         <v>56</v>
       </c>
-      <c r="G102" s="2"/>
-      <c r="H102" s="23" t="s">
+      <c r="G103" s="54"/>
+      <c r="H103" s="21" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="103" spans="1:8">
-      <c r="A103" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C103" s="10"/>
-      <c r="D103" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="E103" s="6">
-        <v>2</v>
-      </c>
-      <c r="F103" s="6">
-        <v>56</v>
-      </c>
-      <c r="G103" s="2"/>
-      <c r="H103" s="21"/>
     </row>
     <row r="104" spans="1:8" ht="31.5" customHeight="1">
       <c r="A104" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C104" s="5"/>
+      <c r="D104" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="E104" s="2">
+        <v>2</v>
+      </c>
+      <c r="F104" s="2">
+        <v>56</v>
+      </c>
+      <c r="G104" s="54"/>
+      <c r="H104" s="32"/>
+    </row>
+    <row r="105" spans="1:8" ht="27">
+      <c r="A105" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="B104" s="6">
+      <c r="B105" s="2">
         <v>90</v>
       </c>
-      <c r="C104" s="10"/>
-      <c r="D104" s="6">
+      <c r="C105" s="5"/>
+      <c r="D105" s="2">
         <v>0.2</v>
       </c>
-      <c r="E104" s="6">
+      <c r="E105" s="2">
         <v>7.5</v>
       </c>
-      <c r="F104" s="6">
+      <c r="F105" s="2">
         <v>29</v>
       </c>
-      <c r="G104" s="12" t="s">
+      <c r="G105" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="H104" s="53" t="s">
+      <c r="H105" s="32" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
-      <c r="A105" s="27" t="s">
+    <row r="106" spans="1:8">
+      <c r="A106" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="B105" s="6">
+      <c r="B106" s="2">
         <v>90</v>
       </c>
-      <c r="C105" s="10"/>
-      <c r="D105" s="6">
+      <c r="C106" s="5"/>
+      <c r="D106" s="2">
         <v>0.8</v>
       </c>
-      <c r="E105" s="6">
+      <c r="E106" s="2">
         <v>1.9</v>
       </c>
-      <c r="F105" s="6">
+      <c r="F106" s="2">
         <v>50</v>
       </c>
-      <c r="G105" s="2"/>
-      <c r="H105" s="23" t="s">
+      <c r="G106" s="54"/>
+      <c r="H106" s="21" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
-      <c r="A106" s="28" t="s">
+    <row r="107" spans="1:8">
+      <c r="A107" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="B106" s="6">
+      <c r="B107" s="2">
         <v>90</v>
       </c>
-      <c r="C106" s="10"/>
-      <c r="D106" s="6">
+      <c r="C107" s="5"/>
+      <c r="D107" s="2">
         <v>1.6</v>
       </c>
-      <c r="E106" s="6">
+      <c r="E107" s="2">
         <v>6</v>
       </c>
-      <c r="F106" s="6">
+      <c r="F107" s="2">
         <v>67</v>
       </c>
-      <c r="G106" s="2"/>
-      <c r="H106" s="23" t="s">
+      <c r="G107" s="54"/>
+      <c r="H107" s="21" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
-      <c r="A107" s="28" t="s">
+    <row r="108" spans="1:8">
+      <c r="A108" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="B107" s="6">
+      <c r="B108" s="2">
         <v>90</v>
       </c>
-      <c r="C107" s="10"/>
-      <c r="D107" s="6">
+      <c r="C108" s="5"/>
+      <c r="D108" s="2">
         <v>1.6</v>
       </c>
-      <c r="E107" s="6">
+      <c r="E108" s="2">
         <v>6</v>
       </c>
-      <c r="F107" s="6">
+      <c r="F108" s="2">
         <v>90</v>
       </c>
-      <c r="G107" s="2"/>
-      <c r="H107" s="23" t="s">
+      <c r="G108" s="54"/>
+      <c r="H108" s="21" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
-      <c r="A108" s="28" t="s">
+    <row r="109" spans="1:8">
+      <c r="A109" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="B108" s="6">
+      <c r="B109" s="2">
         <v>90</v>
       </c>
-      <c r="C108" s="10"/>
-      <c r="D108" s="6">
+      <c r="C109" s="5"/>
+      <c r="D109" s="2">
         <v>0.4</v>
       </c>
-      <c r="E108" s="6">
+      <c r="E109" s="2">
         <v>8</v>
       </c>
-      <c r="F108" s="6">
+      <c r="F109" s="2">
         <v>56</v>
       </c>
-      <c r="G108" s="2"/>
-      <c r="H108" s="23" t="s">
+      <c r="G109" s="54"/>
+      <c r="H109" s="21" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
-      <c r="A109" s="28" t="s">
+    <row r="110" spans="1:8" ht="31.9" customHeight="1">
+      <c r="A110" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="B110" s="2">
+        <v>90</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D110" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="E110" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F110" s="2">
+        <v>30</v>
+      </c>
+      <c r="G110" s="51" t="s">
+        <v>345</v>
+      </c>
+      <c r="H110" s="26" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="30.75" customHeight="1">
+      <c r="A111" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="B111" s="2">
+        <v>90</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D111" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E111" s="2">
+        <v>7</v>
+      </c>
+      <c r="F111" s="2">
+        <v>34</v>
+      </c>
+      <c r="G111" s="54" t="s">
+        <v>346</v>
+      </c>
+      <c r="H111" s="26" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="31.15" customHeight="1">
+      <c r="A112" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="B109" s="6" t="s">
+      <c r="B112" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C109" s="10"/>
-      <c r="D109" s="6">
+      <c r="C112" s="5"/>
+      <c r="D112" s="2">
         <v>0.9</v>
       </c>
-      <c r="E109" s="6">
+      <c r="E112" s="2">
         <v>1.8</v>
       </c>
-      <c r="F109" s="6">
+      <c r="F112" s="2">
         <v>77</v>
       </c>
-      <c r="G109" s="2"/>
-      <c r="H109" s="23" t="s">
+      <c r="G112" s="54"/>
+      <c r="H112" s="21" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="31.9" customHeight="1">
-      <c r="A110" s="42" t="s">
+    <row r="113" spans="1:8" ht="31.15" customHeight="1">
+      <c r="A113" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="B110" s="6">
+      <c r="B113" s="2">
         <v>95</v>
       </c>
-      <c r="C110" s="14" t="s">
+      <c r="C113" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="D110" s="6">
+      <c r="D113" s="2">
         <v>1</v>
       </c>
-      <c r="E110" s="6">
+      <c r="E113" s="2">
         <v>1.9</v>
       </c>
-      <c r="F110" s="6">
+      <c r="F113" s="2">
         <v>46</v>
       </c>
-      <c r="G110" s="2"/>
-      <c r="H110" s="43" t="s">
+      <c r="G113" s="54"/>
+      <c r="H113" s="26" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="30.75" customHeight="1">
-      <c r="A111" s="28" t="s">
+    <row r="114" spans="1:8" ht="31.15" customHeight="1">
+      <c r="A114" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="B111" s="6">
+      <c r="B114" s="2">
         <v>95</v>
       </c>
-      <c r="C111" s="10"/>
-      <c r="D111" s="6">
+      <c r="C114" s="5"/>
+      <c r="D114" s="2">
         <v>1</v>
       </c>
-      <c r="E111" s="6">
+      <c r="E114" s="2">
         <v>2</v>
       </c>
-      <c r="F111" s="6">
+      <c r="F114" s="2">
         <v>40</v>
       </c>
-      <c r="G111" s="2"/>
-      <c r="H111" s="36" t="s">
+      <c r="G114" s="54"/>
+      <c r="H114" s="26" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="31.15" customHeight="1">
-      <c r="A112" s="28" t="s">
+    <row r="115" spans="1:8" ht="31.15" customHeight="1">
+      <c r="A115" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="B112" s="6">
+      <c r="B115" s="2">
         <v>98</v>
       </c>
-      <c r="C112" s="10"/>
-      <c r="D112" s="6">
+      <c r="C115" s="5"/>
+      <c r="D115" s="2">
         <v>0.9</v>
       </c>
-      <c r="E112" s="6">
+      <c r="E115" s="2">
         <v>1.5</v>
       </c>
-      <c r="F112" s="6">
+      <c r="F115" s="2">
         <v>100</v>
       </c>
-      <c r="G112" s="2"/>
-      <c r="H112" s="36" t="s">
+      <c r="G115" s="54"/>
+      <c r="H115" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="31.15" customHeight="1">
-      <c r="A113" s="28" t="s">
+    <row r="116" spans="1:8" ht="33" customHeight="1">
+      <c r="A116" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="B113" s="6">
+      <c r="B116" s="2">
         <v>100</v>
       </c>
-      <c r="C113" s="10"/>
-      <c r="D113" s="6">
+      <c r="C116" s="5"/>
+      <c r="D116" s="2">
         <v>0.8</v>
       </c>
-      <c r="E113" s="6">
+      <c r="E116" s="2">
         <v>2.1</v>
       </c>
-      <c r="F113" s="6">
+      <c r="F116" s="2">
         <v>50</v>
       </c>
-      <c r="G113" s="2"/>
-      <c r="H113" s="36" t="s">
+      <c r="G116" s="54"/>
+      <c r="H116" s="26" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="31.15" customHeight="1">
-      <c r="A114" s="28" t="s">
+    <row r="117" spans="1:8" ht="27">
+      <c r="A117" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="B114" s="6">
+      <c r="B117" s="2">
         <v>100</v>
       </c>
-      <c r="C114" s="10"/>
-      <c r="D114" s="6">
+      <c r="C117" s="5"/>
+      <c r="D117" s="2">
         <v>0.8</v>
       </c>
-      <c r="E114" s="6">
+      <c r="E117" s="2">
         <v>2.1</v>
       </c>
-      <c r="F114" s="6">
+      <c r="F117" s="2">
         <v>72</v>
       </c>
-      <c r="G114" s="2"/>
-      <c r="H114" s="36" t="s">
+      <c r="G117" s="54"/>
+      <c r="H117" s="26" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="31.15" customHeight="1">
-      <c r="A115" s="28" t="s">
+    <row r="118" spans="1:8">
+      <c r="A118" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="B115" s="6">
+      <c r="B118" s="2">
         <v>100</v>
       </c>
-      <c r="C115" s="10"/>
-      <c r="D115" s="6">
+      <c r="C118" s="5"/>
+      <c r="D118" s="2">
         <v>0.9</v>
       </c>
-      <c r="E115" s="6">
+      <c r="E118" s="2">
         <v>1.8</v>
       </c>
-      <c r="F115" s="6">
+      <c r="F118" s="2">
         <v>100</v>
       </c>
-      <c r="G115" s="2"/>
-      <c r="H115" s="43" t="s">
+      <c r="G118" s="54"/>
+      <c r="H118" s="26" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="33" customHeight="1">
-      <c r="A116" s="28" t="s">
+    <row r="119" spans="1:8" ht="27">
+      <c r="A119" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="B116" s="6">
+      <c r="B119" s="2">
         <v>100</v>
       </c>
-      <c r="C116" s="10"/>
-      <c r="D116" s="6">
+      <c r="C119" s="5"/>
+      <c r="D119" s="2">
         <v>0.8</v>
       </c>
-      <c r="E116" s="6">
+      <c r="E119" s="2">
         <v>2</v>
       </c>
-      <c r="F116" s="6">
+      <c r="F119" s="2">
         <v>50</v>
       </c>
-      <c r="G116" s="2"/>
-      <c r="H116" s="36" t="s">
+      <c r="G119" s="54"/>
+      <c r="H119" s="26" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="14.65">
-      <c r="A117" s="28" t="s">
+    <row r="120" spans="1:8" ht="14.25">
+      <c r="A120" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="B117" s="6" t="s">
+      <c r="B120" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C117" s="9" t="s">
+      <c r="C120" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="D117" s="6">
+      <c r="D120" s="2">
         <v>0.8</v>
       </c>
-      <c r="E117" s="6">
+      <c r="E120" s="2">
         <v>2</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F120" s="2">
         <v>46</v>
       </c>
-      <c r="G117" s="2"/>
-      <c r="H117" s="23" t="s">
+      <c r="G120" s="54"/>
+      <c r="H120" s="21" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
-      <c r="A118" s="28" t="s">
+    <row r="121" spans="1:8">
+      <c r="A121" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="B118" s="6">
+      <c r="B121" s="2">
         <v>100</v>
       </c>
-      <c r="C118" s="10"/>
-      <c r="D118" s="6">
+      <c r="C121" s="5"/>
+      <c r="D121" s="2">
         <v>0.9</v>
       </c>
-      <c r="E118" s="6">
+      <c r="E121" s="2">
         <v>1.8</v>
       </c>
-      <c r="F118" s="6">
+      <c r="F121" s="2">
         <v>59</v>
       </c>
-      <c r="G118" s="2"/>
-      <c r="H118" s="23" t="s">
+      <c r="G121" s="54"/>
+      <c r="H121" s="21" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
-      <c r="A119" s="28" t="s">
+    <row r="122" spans="1:8" ht="18.399999999999999" customHeight="1">
+      <c r="A122" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="B119" s="6" t="s">
+      <c r="B122" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C119" s="10"/>
-      <c r="D119" s="6">
+      <c r="C122" s="5"/>
+      <c r="D122" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E119" s="6">
+      <c r="E122" s="2">
         <v>1.6</v>
       </c>
-      <c r="F119" s="6">
+      <c r="F122" s="2">
         <v>72</v>
       </c>
-      <c r="G119" s="2"/>
-      <c r="H119" s="32" t="s">
+      <c r="G122" s="54"/>
+      <c r="H122" s="22" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
-      <c r="A120" s="28" t="s">
+    <row r="123" spans="1:8" ht="31.15" customHeight="1">
+      <c r="A123" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="B120" s="6" t="s">
+      <c r="B123" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C120" s="10"/>
-      <c r="D120" s="6">
+      <c r="C123" s="5"/>
+      <c r="D123" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E120" s="6">
+      <c r="E123" s="2">
         <v>1.8</v>
       </c>
-      <c r="F120" s="6">
+      <c r="F123" s="2">
         <v>77</v>
       </c>
-      <c r="G120" s="2"/>
-      <c r="H120" s="23" t="s">
+      <c r="G123" s="54"/>
+      <c r="H123" s="21" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
-      <c r="A121" s="28" t="s">
+    <row r="124" spans="1:8">
+      <c r="A124" s="16" t="s">
         <v>244</v>
       </c>
-      <c r="B121" s="6">
+      <c r="B124" s="2">
         <v>100</v>
       </c>
-      <c r="C121" s="10"/>
-      <c r="D121" s="6">
+      <c r="C124" s="5"/>
+      <c r="D124" s="2">
         <v>1.3</v>
       </c>
-      <c r="E121" s="6">
+      <c r="E124" s="2">
         <v>1.6</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F124" s="2">
         <v>72</v>
       </c>
-      <c r="G121" s="2"/>
-      <c r="H121" s="23" t="s">
+      <c r="G124" s="54"/>
+      <c r="H124" s="21" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="18.399999999999999" customHeight="1">
-      <c r="A122" s="28" t="s">
+    <row r="125" spans="1:8">
+      <c r="A125" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="B122" s="6">
+      <c r="B125" s="2">
         <v>105</v>
       </c>
-      <c r="C122" s="7" t="s">
+      <c r="C125" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="D122" s="6">
+      <c r="D125" s="2">
         <v>0.8</v>
       </c>
-      <c r="E122" s="6">
+      <c r="E125" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F122" s="6">
+      <c r="F125" s="2">
         <v>46</v>
       </c>
-      <c r="G122" s="2"/>
-      <c r="H122" s="36" t="s">
+      <c r="G125" s="54"/>
+      <c r="H125" s="26" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="31.15" customHeight="1">
-      <c r="A123" s="28" t="s">
+    <row r="126" spans="1:8" ht="27">
+      <c r="A126" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="B123" s="6">
+      <c r="B126" s="2">
         <v>105</v>
       </c>
-      <c r="C123" s="8" t="s">
+      <c r="C126" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="D123" s="6">
+      <c r="D126" s="2">
         <v>0.7</v>
       </c>
-      <c r="E123" s="6">
+      <c r="E126" s="2">
         <v>1.9</v>
       </c>
-      <c r="F123" s="6">
+      <c r="F126" s="2">
         <v>50</v>
       </c>
-      <c r="G123" s="2"/>
-      <c r="H123" s="36" t="s">
+      <c r="G126" s="54"/>
+      <c r="H126" s="26" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
-      <c r="A124" s="27" t="s">
+    <row r="127" spans="1:8">
+      <c r="A127" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="B124" s="6">
+      <c r="B127" s="2">
         <v>107</v>
       </c>
-      <c r="C124" s="10"/>
-      <c r="D124" s="6">
+      <c r="C127" s="5"/>
+      <c r="D127" s="2">
         <v>0.9</v>
       </c>
-      <c r="E124" s="6">
+      <c r="E127" s="2">
         <v>1.9</v>
       </c>
-      <c r="F124" s="6">
+      <c r="F127" s="2">
         <v>67</v>
       </c>
-      <c r="G124" s="2"/>
-      <c r="H124" s="32" t="s">
+      <c r="G127" s="54"/>
+      <c r="H127" s="22" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
-      <c r="A125" s="28" t="s">
+    <row r="128" spans="1:8">
+      <c r="A128" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="B125" s="6">
+      <c r="B128" s="2">
         <v>110</v>
       </c>
-      <c r="C125" s="10"/>
-      <c r="D125" s="6">
+      <c r="C128" s="5"/>
+      <c r="D128" s="2">
         <v>0.9</v>
       </c>
-      <c r="E125" s="6">
+      <c r="E128" s="2">
         <v>2</v>
       </c>
-      <c r="F125" s="6">
+      <c r="F128" s="2">
         <v>67</v>
       </c>
-      <c r="G125" s="2"/>
-      <c r="H125" s="23" t="s">
+      <c r="G128" s="54"/>
+      <c r="H128" s="21" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
-      <c r="A126" s="28" t="s">
+    <row r="129" spans="1:9">
+      <c r="A129" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="B126" s="6">
+      <c r="B129" s="2">
         <v>110</v>
       </c>
-      <c r="C126" s="10"/>
-      <c r="D126" s="6">
+      <c r="C129" s="5"/>
+      <c r="D129" s="2">
         <v>1</v>
       </c>
-      <c r="E126" s="6">
+      <c r="E129" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F126" s="6">
+      <c r="F129" s="2">
         <v>67</v>
       </c>
-      <c r="G126" s="2"/>
-      <c r="H126" s="32" t="s">
+      <c r="G129" s="54"/>
+      <c r="H129" s="22" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
-      <c r="A127" s="28" t="s">
+    <row r="130" spans="1:9" ht="45.75" customHeight="1">
+      <c r="A130" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="B127" s="6">
+      <c r="B130" s="2">
         <v>110</v>
       </c>
-      <c r="C127" s="10"/>
-      <c r="D127" s="6">
+      <c r="C130" s="5"/>
+      <c r="D130" s="2">
         <v>1</v>
       </c>
-      <c r="E127" s="6">
+      <c r="E130" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F127" s="6">
+      <c r="F130" s="2">
         <v>98</v>
       </c>
-      <c r="G127" s="2"/>
-      <c r="H127" s="32" t="s">
+      <c r="G130" s="54"/>
+      <c r="H130" s="22" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
-      <c r="A128" s="28" t="s">
+    <row r="131" spans="1:9">
+      <c r="A131" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="B128" s="6">
+      <c r="B131" s="2">
         <v>112</v>
       </c>
-      <c r="C128" s="10"/>
-      <c r="D128" s="6">
+      <c r="C131" s="5"/>
+      <c r="D131" s="2">
         <v>0.9</v>
       </c>
-      <c r="E128" s="6">
+      <c r="E131" s="2">
         <v>1.5</v>
       </c>
-      <c r="F128" s="6">
+      <c r="F131" s="2">
         <v>50</v>
       </c>
-      <c r="G128" s="2"/>
-      <c r="H128" s="23" t="s">
+      <c r="G131" s="54"/>
+      <c r="H131" s="21" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="40.5">
-      <c r="A129" s="27" t="s">
+    <row r="132" spans="1:9" ht="92.25" customHeight="1">
+      <c r="A132" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="B132" s="2">
+        <v>125</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="D132" s="2">
+        <v>1</v>
+      </c>
+      <c r="E132" s="2">
+        <v>2</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="G132" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="H132" s="26" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="48.75" customHeight="1">
+      <c r="A133" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="B129" s="6" t="s">
+      <c r="B133" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C129" s="10"/>
-      <c r="D129" s="6">
+      <c r="C133" s="5"/>
+      <c r="D133" s="2">
         <v>1</v>
       </c>
-      <c r="E129" s="6">
+      <c r="E133" s="2">
         <v>2</v>
       </c>
-      <c r="F129" s="6">
+      <c r="F133" s="2">
         <v>50</v>
       </c>
-      <c r="G129" s="13" t="s">
+      <c r="G133" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="H129" s="36" t="s">
+      <c r="H133" s="26" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="45.75" customHeight="1">
-      <c r="A130" s="28" t="s">
+    <row r="134" spans="1:9">
+      <c r="A134" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="B130" s="6">
+      <c r="B134" s="2">
         <v>128</v>
       </c>
-      <c r="C130" s="10"/>
-      <c r="D130" s="6">
+      <c r="C134" s="5"/>
+      <c r="D134" s="2">
         <v>0.8</v>
       </c>
-      <c r="E130" s="6">
+      <c r="E134" s="2">
         <v>2</v>
       </c>
-      <c r="F130" s="6">
+      <c r="F134" s="2">
         <v>46</v>
       </c>
-      <c r="G130" s="2"/>
-      <c r="H130" s="23" t="s">
+      <c r="G134" s="54"/>
+      <c r="H134" s="21" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="28.5">
-      <c r="A131" s="44" t="s">
+    <row r="135" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A135" s="65" t="s">
         <v>262</v>
       </c>
-      <c r="B131" s="6" t="s">
+      <c r="B135" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C135" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="D131" s="6">
+      <c r="D135" s="2">
         <v>1</v>
       </c>
-      <c r="E131" s="6">
+      <c r="E135" s="2">
         <v>2</v>
       </c>
-      <c r="F131" s="6">
+      <c r="F135" s="2">
         <v>53</v>
       </c>
-      <c r="G131" s="2"/>
-      <c r="H131" s="37" t="s">
+      <c r="G135" s="54"/>
+      <c r="H135" s="21" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="30" customHeight="1">
-      <c r="A132" s="28" t="s">
+    <row r="136" spans="1:9" ht="34.5" customHeight="1">
+      <c r="A136" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="B132" s="6" t="s">
+      <c r="B136" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C132" s="10"/>
-      <c r="D132" s="6">
+      <c r="C136" s="5"/>
+      <c r="D136" s="2">
         <v>0.8</v>
       </c>
-      <c r="E132" s="6">
+      <c r="E136" s="2">
         <v>2</v>
       </c>
-      <c r="F132" s="6">
+      <c r="F136" s="2">
         <v>46</v>
       </c>
-      <c r="G132" s="2"/>
-      <c r="H132" s="37" t="s">
+      <c r="G136" s="54"/>
+      <c r="H136" s="21" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="17.649999999999999" customHeight="1">
-      <c r="A133" s="28" t="s">
+    <row r="137" spans="1:9" ht="33" customHeight="1">
+      <c r="A137" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="B133" s="6">
+      <c r="B137" s="2">
         <v>130</v>
       </c>
-      <c r="C133" s="10"/>
-      <c r="D133" s="6">
+      <c r="C137" s="5"/>
+      <c r="D137" s="2">
         <v>1</v>
       </c>
-      <c r="E133" s="6">
+      <c r="E137" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F133" s="6">
+      <c r="F137" s="2">
         <v>50</v>
       </c>
-      <c r="G133" s="2"/>
-      <c r="H133" s="32" t="s">
+      <c r="G137" s="54"/>
+      <c r="H137" s="22" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="27">
-      <c r="A134" s="28" t="s">
+    <row r="138" spans="1:9" ht="27">
+      <c r="A138" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="B134" s="6">
+      <c r="B138" s="2">
         <v>132</v>
       </c>
-      <c r="C134" s="10"/>
-      <c r="D134" s="6">
+      <c r="C138" s="5"/>
+      <c r="D138" s="2">
         <v>0.8</v>
       </c>
-      <c r="E134" s="6">
+      <c r="E138" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F134" s="6">
+      <c r="F138" s="2">
         <v>50</v>
       </c>
-      <c r="G134" s="2"/>
-      <c r="H134" s="36" t="s">
+      <c r="G138" s="54"/>
+      <c r="H138" s="26" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A135" s="28" t="s">
+    <row r="139" spans="1:9" ht="27">
+      <c r="A139" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="B135" s="6">
+      <c r="B139" s="2">
         <v>132</v>
       </c>
-      <c r="C135" s="10"/>
-      <c r="D135" s="6">
+      <c r="C139" s="5"/>
+      <c r="D139" s="2">
         <v>0.8</v>
       </c>
-      <c r="E135" s="6">
+      <c r="E139" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F135" s="6">
+      <c r="F139" s="2">
         <v>46</v>
       </c>
-      <c r="G135" s="2"/>
-      <c r="H135" s="36" t="s">
+      <c r="G139" s="54"/>
+      <c r="H139" s="26" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="34.5" customHeight="1">
-      <c r="A136" s="28" t="s">
+    <row r="140" spans="1:9" ht="27">
+      <c r="A140" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="B136" s="6">
+      <c r="B140" s="2">
         <v>132</v>
       </c>
-      <c r="C136" s="10"/>
-      <c r="D136" s="6">
+      <c r="C140" s="5"/>
+      <c r="D140" s="2">
         <v>0.8</v>
       </c>
-      <c r="E136" s="6">
+      <c r="E140" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F136" s="6">
+      <c r="F140" s="2">
         <v>63</v>
       </c>
-      <c r="G136" s="2"/>
-      <c r="H136" s="36" t="s">
+      <c r="G140" s="54"/>
+      <c r="H140" s="26" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="33" customHeight="1">
-      <c r="A137" s="47" t="s">
+    <row r="141" spans="1:9">
+      <c r="A141" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="B137" s="48" t="s">
+      <c r="B141" s="29" t="s">
         <v>273</v>
       </c>
-      <c r="C137" s="49"/>
-      <c r="D137" s="48">
+      <c r="C141" s="30"/>
+      <c r="D141" s="29">
         <v>0.8</v>
       </c>
-      <c r="E137" s="48">
+      <c r="E141" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F137" s="48">
+      <c r="F141" s="29">
         <v>50</v>
       </c>
-      <c r="G137" s="54"/>
-      <c r="H137" s="50" t="s">
+      <c r="G141" s="66"/>
+      <c r="H141" s="67" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="138" spans="1:9">
-      <c r="A138" s="28" t="s">
+      <c r="I141" s="47"/>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="B138" s="6">
+      <c r="B142" s="2">
         <v>150</v>
       </c>
-      <c r="C138" s="10"/>
-      <c r="D138" s="6">
+      <c r="C142" s="5"/>
+      <c r="D142" s="2">
         <v>0.5</v>
       </c>
-      <c r="E138" s="6">
+      <c r="E142" s="2">
         <v>7</v>
       </c>
-      <c r="F138" s="6">
+      <c r="F142" s="2">
         <v>100</v>
       </c>
-      <c r="G138" s="2"/>
-      <c r="H138" s="23" t="s">
+      <c r="G142" s="54"/>
+      <c r="H142" s="21" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="27">
-      <c r="A139" s="61" t="s">
+    <row r="143" spans="1:9" ht="27">
+      <c r="A143" s="39" t="s">
         <v>304</v>
       </c>
-      <c r="B139" s="55" t="s">
+      <c r="B143" s="33" t="s">
         <v>324</v>
       </c>
-      <c r="C139" s="49"/>
-      <c r="D139" s="55">
+      <c r="C143" s="30"/>
+      <c r="D143" s="33">
         <v>1</v>
       </c>
-      <c r="E139" s="55">
+      <c r="E143" s="33">
         <v>2</v>
       </c>
-      <c r="F139" s="55">
+      <c r="F143" s="33">
         <v>143</v>
       </c>
-      <c r="G139" s="54"/>
-      <c r="H139" s="72" t="s">
+      <c r="G143" s="66"/>
+      <c r="H143" s="48" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="27">
-      <c r="A140" s="62" t="s">
+    <row r="144" spans="1:9" ht="27">
+      <c r="A144" s="40" t="s">
         <v>318</v>
       </c>
-      <c r="B140" s="56" t="s">
+      <c r="B144" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="C140" s="57" t="s">
+      <c r="C144" s="35" t="s">
         <v>322</v>
       </c>
-      <c r="D140" s="56" t="s">
+      <c r="D144" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="E140" s="56">
+      <c r="E144" s="34">
         <v>5</v>
       </c>
-      <c r="F140" s="56">
+      <c r="F144" s="34">
         <v>1</v>
       </c>
-      <c r="G140" s="59" t="s">
+      <c r="G144" s="37" t="s">
         <v>323</v>
       </c>
-      <c r="H140" s="70" t="s">
+      <c r="H144" s="48" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
-      <c r="A141" s="63" t="s">
+    <row r="145" spans="1:8">
+      <c r="A145" s="41" t="s">
         <v>319</v>
       </c>
-      <c r="B141" s="58">
+      <c r="B145" s="36">
         <v>35</v>
       </c>
-      <c r="C141" s="60"/>
-      <c r="D141" s="58" t="s">
+      <c r="C145" s="38"/>
+      <c r="D145" s="36" t="s">
         <v>321</v>
       </c>
-      <c r="E141" s="58">
+      <c r="E145" s="36">
         <v>5</v>
       </c>
-      <c r="F141" s="58">
+      <c r="F145" s="36">
         <v>1</v>
       </c>
-      <c r="G141" s="54"/>
-      <c r="H141" s="64" t="s">
+      <c r="G145" s="66"/>
+      <c r="H145" s="42" t="s">
         <v>326</v>
       </c>
-      <c r="I141" s="69"/>
-    </row>
-    <row r="142" spans="1:9" ht="13.9" thickBot="1">
-      <c r="A142" s="65" t="s">
+    </row>
+    <row r="146" spans="1:8" ht="13.9" thickBot="1">
+      <c r="A146" s="43" t="s">
         <v>320</v>
       </c>
-      <c r="B142" s="66">
+      <c r="B146" s="44">
         <v>20</v>
       </c>
-      <c r="C142" s="67" t="s">
+      <c r="C146" s="45" t="s">
         <v>165</v>
       </c>
-      <c r="D142" s="66" t="s">
+      <c r="D146" s="44" t="s">
         <v>321</v>
       </c>
-      <c r="E142" s="66">
+      <c r="E146" s="44">
         <v>4</v>
       </c>
-      <c r="F142" s="66">
+      <c r="F146" s="44">
         <v>1</v>
       </c>
-      <c r="G142" s="54"/>
-      <c r="H142" s="68" t="s">
+      <c r="G146" s="66"/>
+      <c r="H146" s="46" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5515,20 +5664,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5751,14 +5900,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -5771,6 +5912,14 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7789893-6744-4DCF-BB89-6BFF62866AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB21F40-5778-4FAF-B598-9DAD3084AFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -1095,9 +1095,6 @@
     <t>击杀敌人会对能见范围内所有敌人造成周期性火焰伤害200点，即4*50点燃</t>
   </si>
   <si>
-    <t>击中目标时，持续5秒，一共造成200点火焰伤害，即5*40点燃</t>
-  </si>
-  <si>
     <t>元素熔炉配方：被咒棒子*1 大型火焰精华*20 硝酸钾*20 4级火焰卷轴*2</t>
   </si>
   <si>
@@ -1114,6 +1111,9 @@
   </si>
   <si>
     <t>每次攻击都会给自己叠加一层点燃，每层持续37秒，造成 20*3共60点火焰伤害。身上每有一层点燃，这把武器的火焰伤害就+3。举例：以每秒一次的频率持续攻击，可稳定维持37层，武器火焰伤害从60提升到171，同时你自己每秒承受约60点点燃伤害。若攻击37秒后停手，最后一层还要再烧37秒，累计自伤2220点。全套冰霜护甲可做到不受任何点燃伤害。</t>
+  </si>
+  <si>
+    <t>击中目标时，持续5秒，一共造成200点火焰伤害，即5*40点燃；远程武器</t>
   </si>
 </sst>
 </file>
@@ -1798,7 +1798,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1966,8 +1966,26 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1976,27 +1994,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2352,16 +2349,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21.4" thickBot="1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="60"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="9" t="s">
@@ -2403,12 +2400,12 @@
       <c r="E3" s="55">
         <v>1</v>
       </c>
-      <c r="F3" s="61"/>
+      <c r="F3" s="57"/>
       <c r="G3" s="54"/>
       <c r="H3" s="32"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="58" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="53" t="s">
@@ -2684,7 +2681,7 @@
       <c r="G15" s="54" t="s">
         <v>307</v>
       </c>
-      <c r="H15" s="63" t="s">
+      <c r="H15" s="59" t="s">
         <v>301</v>
       </c>
     </row>
@@ -2771,7 +2768,7 @@
       <c r="F19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="57" t="s">
+      <c r="G19" s="6" t="s">
         <v>336</v>
       </c>
       <c r="H19" s="21" t="s">
@@ -2886,7 +2883,7 @@
       <c r="G24" s="54" t="s">
         <v>307</v>
       </c>
-      <c r="H24" s="63" t="s">
+      <c r="H24" s="59" t="s">
         <v>300</v>
       </c>
     </row>
@@ -4186,7 +4183,7 @@
       <c r="G81" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="H81" s="64"/>
+      <c r="H81" s="60"/>
     </row>
     <row r="82" spans="1:8" ht="33" customHeight="1">
       <c r="A82" s="15" t="s">
@@ -4451,7 +4448,7 @@
       <c r="F93" s="2">
         <v>46</v>
       </c>
-      <c r="G93" s="57" t="s">
+      <c r="G93" s="6" t="s">
         <v>340</v>
       </c>
       <c r="H93" s="22" t="s">
@@ -4830,7 +4827,7 @@
         <v>30</v>
       </c>
       <c r="G110" s="51" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H110" s="26" t="s">
         <v>343</v>
@@ -4856,10 +4853,10 @@
         <v>34</v>
       </c>
       <c r="G111" s="54" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H111" s="26" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="31.15" customHeight="1">
@@ -5312,13 +5309,13 @@
     </row>
     <row r="132" spans="1:9" ht="92.25" customHeight="1">
       <c r="A132" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B132" s="2">
         <v>125</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D132" s="2">
         <v>1</v>
@@ -5330,10 +5327,10 @@
         <v>334</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="H132" s="26" t="s">
         <v>349</v>
-      </c>
-      <c r="H132" s="26" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="48.75" customHeight="1">
@@ -5383,7 +5380,7 @@
       </c>
     </row>
     <row r="135" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A135" s="65" t="s">
+      <c r="A135" s="61" t="s">
         <v>262</v>
       </c>
       <c r="B135" s="2" t="s">
@@ -5533,8 +5530,8 @@
       <c r="F141" s="29">
         <v>50</v>
       </c>
-      <c r="G141" s="66"/>
-      <c r="H141" s="67" t="s">
+      <c r="G141" s="62"/>
+      <c r="H141" s="63" t="s">
         <v>274</v>
       </c>
       <c r="I141" s="47"/>
@@ -5561,7 +5558,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="27">
+    <row r="143" spans="1:9">
       <c r="A143" s="39" t="s">
         <v>304</v>
       </c>
@@ -5578,7 +5575,7 @@
       <c r="F143" s="33">
         <v>143</v>
       </c>
-      <c r="G143" s="66"/>
+      <c r="G143" s="62"/>
       <c r="H143" s="48" t="s">
         <v>325</v>
       </c>
@@ -5626,7 +5623,7 @@
       <c r="F145" s="36">
         <v>1</v>
       </c>
-      <c r="G145" s="66"/>
+      <c r="G145" s="62"/>
       <c r="H145" s="42" t="s">
         <v>326</v>
       </c>
@@ -5650,7 +5647,7 @@
       <c r="F146" s="44">
         <v>1</v>
       </c>
-      <c r="G146" s="66"/>
+      <c r="G146" s="62"/>
       <c r="H146" s="46" t="s">
         <v>327</v>
       </c>
@@ -5664,20 +5661,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5900,6 +5897,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -5912,14 +5917,6 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB21F40-5778-4FAF-B598-9DAD3084AFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F5EC13-76DF-4476-B93A-17B4A8975CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -5661,23 +5661,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F24FF01B6E691B418AC7A3AA007394EC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="59dca28e393f34dbf2d8416fcf89659e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8f43ef-8ea4-412d-9c18-5388ad596486" xmlns:ns4="c1e77170-3c0a-491c-a033-5a7c184eabd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9fc4d359a4793fb93aa5c6a1e92df795" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
@@ -5896,10 +5879,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E7059C5-FC20-439B-9607-B11AF63F0499}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
+    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5922,20 +5933,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E7059C5-FC20-439B-9607-B11AF63F0499}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
-    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F5EC13-76DF-4476-B93A-17B4A8975CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A443E487-E561-46C9-B938-E96DC256E1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="351">
   <si>
     <t>武器</t>
   </si>
@@ -5323,8 +5323,8 @@
       <c r="E132" s="2">
         <v>2</v>
       </c>
-      <c r="F132" s="2" t="s">
-        <v>334</v>
+      <c r="F132" s="2">
+        <v>59</v>
       </c>
       <c r="G132" s="6" t="s">
         <v>348</v>
@@ -5661,6 +5661,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F24FF01B6E691B418AC7A3AA007394EC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="59dca28e393f34dbf2d8416fcf89659e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8f43ef-8ea4-412d-9c18-5388ad596486" xmlns:ns4="c1e77170-3c0a-491c-a033-5a7c184eabd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9fc4d359a4793fb93aa5c6a1e92df795" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
@@ -5879,14 +5887,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5897,6 +5897,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
+    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E7059C5-FC20-439B-9607-B11AF63F0499}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5915,23 +5932,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
-    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
   <ds:schemaRefs>

--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A443E487-E561-46C9-B938-E96DC256E1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC19FBB-4087-4478-B5DE-B2D7A8B29DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="350">
   <si>
     <t>武器</t>
   </si>
@@ -1059,9 +1059,6 @@
   </si>
   <si>
     <t>10 火伤</t>
-  </si>
-  <si>
-    <t>待测</t>
   </si>
   <si>
     <t>杀死敌人后，造成额外2点火焰伤害，持续20秒，这20秒内每杀一个敌人，火焰伤害就增加2，20秒后回到初始的10点</t>
@@ -2769,7 +2766,7 @@
         <v>13</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H19" s="21" t="s">
         <v>49</v>
@@ -2903,14 +2900,14 @@
       <c r="E25" s="8">
         <v>1.2</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="8">
+        <v>100</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="H25" s="50" t="s">
         <v>334</v>
-      </c>
-      <c r="G25" s="51" t="s">
-        <v>337</v>
-      </c>
-      <c r="H25" s="50" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3293,7 +3290,7 @@
         <v>46</v>
       </c>
       <c r="G42" s="54" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H42" s="21" t="s">
         <v>313</v>
@@ -3867,7 +3864,7 @@
         <v>67</v>
       </c>
       <c r="G67" s="51" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H67" s="21" t="s">
         <v>145</v>
@@ -4449,7 +4446,7 @@
         <v>46</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H93" s="22" t="s">
         <v>199</v>
@@ -4809,7 +4806,7 @@
     </row>
     <row r="110" spans="1:8" ht="31.9" customHeight="1">
       <c r="A110" s="16" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B110" s="2">
         <v>90</v>
@@ -4827,15 +4824,15 @@
         <v>30</v>
       </c>
       <c r="G110" s="51" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H110" s="26" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="30.75" customHeight="1">
       <c r="A111" s="16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B111" s="2">
         <v>90</v>
@@ -4853,10 +4850,10 @@
         <v>34</v>
       </c>
       <c r="G111" s="54" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H111" s="26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="31.15" customHeight="1">
@@ -5309,13 +5306,13 @@
     </row>
     <row r="132" spans="1:9" ht="92.25" customHeight="1">
       <c r="A132" s="16" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B132" s="2">
         <v>125</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D132" s="2">
         <v>1</v>
@@ -5327,10 +5324,10 @@
         <v>59</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="H132" s="26" t="s">
         <v>348</v>
-      </c>
-      <c r="H132" s="26" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="48.75" customHeight="1">
@@ -5661,14 +5658,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F24FF01B6E691B418AC7A3AA007394EC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="59dca28e393f34dbf2d8416fcf89659e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8f43ef-8ea4-412d-9c18-5388ad596486" xmlns:ns4="c1e77170-3c0a-491c-a033-5a7c184eabd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9fc4d359a4793fb93aa5c6a1e92df795" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
@@ -5887,6 +5876,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5897,23 +5894,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
-    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E7059C5-FC20-439B-9607-B11AF63F0499}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5932,6 +5912,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
+    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
   <ds:schemaRefs>

--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC19FBB-4087-4478-B5DE-B2D7A8B29DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD1A7DC-A69D-4C16-A07F-52E9A6774DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -1107,10 +1107,25 @@
     <t>元素熔炉配方：狂战士战斧*1 大型火焰精华*20 硝酸钾*20 纯银*20</t>
   </si>
   <si>
-    <t>每次攻击都会给自己叠加一层点燃，每层持续37秒，造成 20*3共60点火焰伤害。身上每有一层点燃，这把武器的火焰伤害就+3。举例：以每秒一次的频率持续攻击，可稳定维持37层，武器火焰伤害从60提升到171，同时你自己每秒承受约60点点燃伤害。若攻击37秒后停手，最后一层还要再烧37秒，累计自伤2220点。全套冰霜护甲可做到不受任何点燃伤害。</t>
-  </si>
-  <si>
     <t>击中目标时，持续5秒，一共造成200点火焰伤害，即5*40点燃；远程武器</t>
+  </si>
+  <si>
+    <t>【武器介绍】每次攻击给自身叠加一层点燃，每层持续37秒，共20跳，每跳3点，合计60点火焰伤害。每有一层点燃，武器火焰伤害+3。由于每层持续37秒，身上的点燃层数等于最近37秒内的攻击次数。攻速越快，层数越高。例如每秒攻击一次时，稳定在37层，武器火焰伤害由60升至171，自身每秒承受约60点点燃伤害；攻击37秒后停手，累计自伤2220点。攻速更快时，37秒内攻击次数超过37次，层数随之超过37层，武器伤害与自伤相应提高。
+【如何免疫自伤】游戏中的伤害只取整数，计算结果带小数时一律向下取整，即直接舍去小数部分，不四舍五入。例如1.98取整为1，0.99取整为0。护甲、药膏、技能的减伤分别结算，每结算一次即向下取整一次。点燃每跳只有3点，经过数次取整降到0，便不再掉血。与层数无关，每一层均为0。注意护甲的减伤率 = 护甲 ÷ (护甲 + 165)
+【40火防 + 坚持药膏 + 1级火焰防御技能】
+护甲：40火防减伤19.51%，3 × (1 − 0.1951) = 2.41，向下取整为2
+坚持药膏减伤20%：2 × 0.8 = 1.6，向下取整为1
+技能减伤1%：1 × 0.99 = 0.99，向下取整为0
+40火防为一个火包。
+【85火防 + 1级火焰防御技能】
+护甲：85火防减伤34%，3 × 0.66 = 1.98，向下取整为1
+技能减伤1%：1 × 0.99 = 0.99，向下取整为0
+85火防约为衣服或裤子，加手套、头盔、鞋子其中一件。
+【40火防 + 蓝色防御药膏 + 1级火焰防御技能】
+同样可以免疫。蓝色防御药膏持续30秒。
+【80火防 + 1级火焰防御技能：无法免疫】
+护甲：80火防减伤32.65%，3 × 0.6735 = 2.02，向下取整为2
+技能减伤1%：2 × 0.99 = 1.98，向下取整为1，仍然每跳损失1点生命。</t>
   </si>
 </sst>
 </file>
@@ -2342,7 +2357,7 @@
     <col min="2" max="2" width="16.46484375" customWidth="1"/>
     <col min="3" max="3" width="10.59765625" customWidth="1"/>
     <col min="7" max="7" width="52.6640625" customWidth="1"/>
-    <col min="8" max="8" width="59" customWidth="1"/>
+    <col min="8" max="8" width="95.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21.4" thickBot="1">
@@ -3296,7 +3311,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27">
+    <row r="43" spans="1:8" ht="14.25">
       <c r="A43" s="49" t="s">
         <v>291</v>
       </c>
@@ -4853,7 +4868,7 @@
         <v>344</v>
       </c>
       <c r="H111" s="26" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="31.15" customHeight="1">
@@ -5304,7 +5319,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="92.25" customHeight="1">
+    <row r="132" spans="1:9" ht="409.5" customHeight="1">
       <c r="A132" s="16" t="s">
         <v>345</v>
       </c>
@@ -5327,7 +5342,7 @@
         <v>347</v>
       </c>
       <c r="H132" s="26" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="48.75" customHeight="1">
@@ -5577,7 +5592,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="27">
+    <row r="144" spans="1:9">
       <c r="A144" s="40" t="s">
         <v>318</v>
       </c>
